--- a/data.mn/public/datasets/mongolbank-international-investment.xlsx
+++ b/data.mn/public/datasets/mongolbank-international-investment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,8 +414,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -506,6 +537,9 @@
       <c r="AB1" t="n">
         <v>2025</v>
       </c>
+      <c r="AC1" t="n">
+        <v>2026</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -594,7 +628,10 @@
         <v>-42015.888</v>
       </c>
       <c r="AB2" t="n">
-        <v>-45167.5</v>
+        <v>-44970.632</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-45914.243</v>
       </c>
     </row>
     <row r="3">
@@ -684,7 +721,10 @@
         <v>-42362.592</v>
       </c>
       <c r="AB3" t="n">
-        <v>-46015.772</v>
+        <v>-45716.876</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-45715.098</v>
       </c>
     </row>
     <row r="4">
@@ -774,7 +814,7 @@
         <v>-42914.651</v>
       </c>
       <c r="AB4" t="n">
-        <v>-45651.362</v>
+        <v>-46290.529</v>
       </c>
     </row>
     <row r="5">
@@ -864,7 +904,7 @@
         <v>-43839.052</v>
       </c>
       <c r="AB5" t="n">
-        <v>-45905.123</v>
+        <v>-46235.965</v>
       </c>
     </row>
     <row r="6">
@@ -954,7 +994,10 @@
         <v>8999.644</v>
       </c>
       <c r="AB6" t="n">
-        <v>9361.471</v>
+        <v>9403.718000000001</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>13479.32</v>
       </c>
     </row>
     <row r="7">
@@ -1044,7 +1087,10 @@
         <v>8896.481</v>
       </c>
       <c r="AB7" t="n">
-        <v>10127.953</v>
+        <v>9841.242</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>13584.524</v>
       </c>
     </row>
     <row r="8">
@@ -1134,7 +1180,7 @@
         <v>9223.344999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>11889.099</v>
+        <v>11152.154</v>
       </c>
     </row>
     <row r="9">
@@ -1224,7 +1270,7 @@
         <v>9859.061</v>
       </c>
       <c r="AB9" t="n">
-        <v>12718.244</v>
+        <v>12333.549</v>
       </c>
     </row>
     <row r="10">
@@ -1314,7 +1360,10 @@
         <v>51015.532</v>
       </c>
       <c r="AB10" t="n">
-        <v>54528.972</v>
+        <v>54374.35</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>59393.563</v>
       </c>
     </row>
     <row r="11">
@@ -1404,7 +1453,10 @@
         <v>51259.073</v>
       </c>
       <c r="AB11" t="n">
-        <v>56143.726</v>
+        <v>55558.119</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>59299.622</v>
       </c>
     </row>
     <row r="12">
@@ -1494,7 +1546,7 @@
         <v>52137.996</v>
       </c>
       <c r="AB12" t="n">
-        <v>57540.461</v>
+        <v>57442.683</v>
       </c>
     </row>
     <row r="13">
@@ -1584,7 +1636,7 @@
         <v>53698.113</v>
       </c>
       <c r="AB13" t="n">
-        <v>58623.367</v>
+        <v>58569.514</v>
       </c>
     </row>
   </sheetData>
@@ -1598,8 +1650,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1690,6 +1773,9 @@
       <c r="AB1" t="n">
         <v>2025</v>
       </c>
+      <c r="AC1" t="n">
+        <v>2026</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1778,7 +1864,10 @@
         <v>-42015.888</v>
       </c>
       <c r="AB2" t="n">
-        <v>-45167.5</v>
+        <v>-44970.632</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-45914.243</v>
       </c>
     </row>
     <row r="3">
@@ -1868,7 +1957,10 @@
         <v>-42362.592</v>
       </c>
       <c r="AB3" t="n">
-        <v>-46015.772</v>
+        <v>-45716.876</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-45715.098</v>
       </c>
     </row>
     <row r="4">
@@ -1958,7 +2050,7 @@
         <v>-42914.651</v>
       </c>
       <c r="AB4" t="n">
-        <v>-45651.362</v>
+        <v>-46290.529</v>
       </c>
     </row>
     <row r="5">
@@ -2048,7 +2140,7 @@
         <v>-43839.052</v>
       </c>
       <c r="AB5" t="n">
-        <v>-45905.123</v>
+        <v>-46235.965</v>
       </c>
     </row>
     <row r="6">
@@ -2138,7 +2230,10 @@
         <v>8999.644</v>
       </c>
       <c r="AB6" t="n">
-        <v>9361.471</v>
+        <v>9403.718000000001</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>13479.32</v>
       </c>
     </row>
     <row r="7">
@@ -2228,7 +2323,10 @@
         <v>8896.481</v>
       </c>
       <c r="AB7" t="n">
-        <v>10127.953</v>
+        <v>9841.242</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>13584.524</v>
       </c>
     </row>
     <row r="8">
@@ -2318,7 +2416,7 @@
         <v>9223.344999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>11889.099</v>
+        <v>11152.154</v>
       </c>
     </row>
     <row r="9">
@@ -2408,7 +2506,7 @@
         <v>9859.061</v>
       </c>
       <c r="AB9" t="n">
-        <v>12718.244</v>
+        <v>12333.549</v>
       </c>
     </row>
     <row r="10">
@@ -2498,7 +2596,10 @@
         <v>51015.532</v>
       </c>
       <c r="AB10" t="n">
-        <v>54528.972</v>
+        <v>54374.35</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>59393.563</v>
       </c>
     </row>
     <row r="11">
@@ -2588,7 +2689,10 @@
         <v>51259.073</v>
       </c>
       <c r="AB11" t="n">
-        <v>56143.726</v>
+        <v>55558.119</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>59299.622</v>
       </c>
     </row>
     <row r="12">
@@ -2678,7 +2782,7 @@
         <v>52137.996</v>
       </c>
       <c r="AB12" t="n">
-        <v>57540.461</v>
+        <v>57442.683</v>
       </c>
     </row>
     <row r="13">
@@ -2768,7 +2872,7 @@
         <v>53698.113</v>
       </c>
       <c r="AB13" t="n">
-        <v>58623.367</v>
+        <v>58569.514</v>
       </c>
     </row>
   </sheetData>
